--- a/artfynd/A 14196-2026 artfynd.xlsx
+++ b/artfynd/A 14196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,3419 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132058261</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>493318</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7027671</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>igenvuxen betesmark?</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132058268</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91837</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493342</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7027483</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132058269</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493330</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7027506</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132058267</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91861</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493397</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7027483</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132058220</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83249</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493217</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7027536</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132058249</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493151</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7027766</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132058215</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493293</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7027489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132058232</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493125</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7027673</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132058242</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>493069</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027751</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132058240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493016</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7027726</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132058255</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80374</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7027701</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132058235</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493016</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7027677</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132058263</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80374</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>493339</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7027668</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>igenvuxen betesmark?</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132058228</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79026</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>493154</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7027631</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132058259</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>493318</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7027653</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132058265</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>493521</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7027520</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132058252</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>493154</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7027820</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132058239</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>492984</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7027718</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132058221</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>493217</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7027549</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132058244</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>493117</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7027728</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132058247</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>493186</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7027738</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132058248</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>493167</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7027755</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132058254</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>493364</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7027770</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132058270</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>493316</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7027545</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132058238</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80374</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>492985</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7027718</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132058222</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>493191</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7027571</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132058217</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>493218</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7027522</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132058218</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>493211</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7027521</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132058241</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>493051</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7027730</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132058230</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>493129</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7027667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132058226</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>hårkmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>493151</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7027627</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14196-2026 artfynd.xlsx
+++ b/artfynd/A 14196-2026 artfynd.xlsx
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132058249</v>
+        <v>132058242</v>
       </c>
       <c r="B8" t="n">
         <v>57907</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493151</v>
+        <v>493069</v>
       </c>
       <c r="R8" t="n">
-        <v>7027766</v>
+        <v>7027751</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132058215</v>
+        <v>132058232</v>
       </c>
       <c r="B9" t="n">
-        <v>57907</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,42 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493293</v>
+        <v>493125</v>
       </c>
       <c r="R9" t="n">
-        <v>7027489</v>
+        <v>7027673</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132058232</v>
+        <v>132058249</v>
       </c>
       <c r="B10" t="n">
-        <v>79269</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493125</v>
+        <v>493151</v>
       </c>
       <c r="R10" t="n">
-        <v>7027673</v>
+        <v>7027766</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132058242</v>
+        <v>132058215</v>
       </c>
       <c r="B11" t="n">
         <v>57907</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493069</v>
+        <v>493293</v>
       </c>
       <c r="R11" t="n">
-        <v>7027751</v>
+        <v>7027489</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132058235</v>
+        <v>132058263</v>
       </c>
       <c r="B14" t="n">
-        <v>79269</v>
+        <v>80374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493016</v>
+        <v>493339</v>
       </c>
       <c r="R14" t="n">
-        <v>7027677</v>
+        <v>7027668</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,6 +2095,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>igenvuxen betesmark?</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2111,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132058263</v>
+        <v>132058235</v>
       </c>
       <c r="B15" t="n">
-        <v>80374</v>
+        <v>79269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493339</v>
+        <v>493016</v>
       </c>
       <c r="R15" t="n">
-        <v>7027668</v>
+        <v>7027677</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2181,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,11 +2207,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>igenvuxen betesmark?</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132058228</v>
+        <v>132058259</v>
       </c>
       <c r="B16" t="n">
-        <v>79026</v>
+        <v>57907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,37 +2234,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493154</v>
+        <v>493318</v>
       </c>
       <c r="R16" t="n">
-        <v>7027631</v>
+        <v>7027653</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,22 +2308,22 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2335,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132058259</v>
+        <v>132058228</v>
       </c>
       <c r="B17" t="n">
-        <v>57907</v>
+        <v>79026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,42 +2351,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493318</v>
+        <v>493154</v>
       </c>
       <c r="R17" t="n">
-        <v>7027653</v>
+        <v>7027631</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2559,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132058252</v>
+        <v>132058244</v>
       </c>
       <c r="B19" t="n">
         <v>79269</v>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493154</v>
+        <v>493117</v>
       </c>
       <c r="R19" t="n">
-        <v>7027820</v>
+        <v>7027728</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,32 +2666,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132058239</v>
+        <v>132058252</v>
       </c>
       <c r="B20" t="n">
-        <v>80403</v>
+        <v>79269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492984</v>
+        <v>493154</v>
       </c>
       <c r="R20" t="n">
-        <v>7027718</v>
+        <v>7027820</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,32 +2773,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132058221</v>
+        <v>132058239</v>
       </c>
       <c r="B21" t="n">
-        <v>79269</v>
+        <v>80403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493217</v>
+        <v>492984</v>
       </c>
       <c r="R21" t="n">
-        <v>7027549</v>
+        <v>7027718</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,7 +2880,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132058244</v>
+        <v>132058221</v>
       </c>
       <c r="B22" t="n">
         <v>79269</v>
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493117</v>
+        <v>493217</v>
       </c>
       <c r="R22" t="n">
-        <v>7027728</v>
+        <v>7027549</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3552,7 +3552,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132058222</v>
+        <v>132058217</v>
       </c>
       <c r="B28" t="n">
         <v>79269</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493191</v>
+        <v>493218</v>
       </c>
       <c r="R28" t="n">
-        <v>7027571</v>
+        <v>7027522</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3659,7 +3659,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132058217</v>
+        <v>132058222</v>
       </c>
       <c r="B29" t="n">
         <v>79269</v>
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493218</v>
+        <v>493191</v>
       </c>
       <c r="R29" t="n">
-        <v>7027522</v>
+        <v>7027571</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3766,7 +3766,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132058218</v>
+        <v>132058241</v>
       </c>
       <c r="B30" t="n">
         <v>79269</v>
@@ -3801,13 +3801,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493211</v>
+        <v>493051</v>
       </c>
       <c r="R30" t="n">
-        <v>7027521</v>
+        <v>7027730</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,7 +3873,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132058241</v>
+        <v>132058230</v>
       </c>
       <c r="B31" t="n">
         <v>79269</v>
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493051</v>
+        <v>493129</v>
       </c>
       <c r="R31" t="n">
-        <v>7027730</v>
+        <v>7027667</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3964,6 +3964,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3980,7 +3985,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132058230</v>
+        <v>132058226</v>
       </c>
       <c r="B32" t="n">
         <v>79269</v>
@@ -4015,13 +4020,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493129</v>
+        <v>493151</v>
       </c>
       <c r="R32" t="n">
-        <v>7027667</v>
+        <v>7027627</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4055,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4065,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4071,11 +4076,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4092,7 +4092,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132058226</v>
+        <v>132058218</v>
       </c>
       <c r="B33" t="n">
         <v>79269</v>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493151</v>
+        <v>493211</v>
       </c>
       <c r="R33" t="n">
-        <v>7027627</v>
+        <v>7027521</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 14196-2026 artfynd.xlsx
+++ b/artfynd/A 14196-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>132058261</v>
       </c>
       <c r="B3" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132058268</v>
+        <v>132058269</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493342</v>
+        <v>493330</v>
       </c>
       <c r="R4" t="n">
-        <v>7027483</v>
+        <v>7027506</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132058269</v>
+        <v>132058268</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>91842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493330</v>
+        <v>493342</v>
       </c>
       <c r="R5" t="n">
-        <v>7027506</v>
+        <v>7027483</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>132058267</v>
       </c>
       <c r="B6" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>132058220</v>
       </c>
       <c r="B7" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132058242</v>
+        <v>132058232</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,42 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493069</v>
+        <v>493125</v>
       </c>
       <c r="R8" t="n">
-        <v>7027751</v>
+        <v>7027673</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132058232</v>
+        <v>132058242</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1440,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493125</v>
+        <v>493069</v>
       </c>
       <c r="R9" t="n">
-        <v>7027673</v>
+        <v>7027751</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
         <v>132058249</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>132058215</v>
       </c>
       <c r="B11" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>132058240</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>132058255</v>
       </c>
       <c r="B13" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>132058263</v>
       </c>
       <c r="B14" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>132058235</v>
       </c>
       <c r="B15" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132058259</v>
+        <v>132058228</v>
       </c>
       <c r="B16" t="n">
-        <v>57907</v>
+        <v>79031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,42 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493318</v>
+        <v>493154</v>
       </c>
       <c r="R16" t="n">
-        <v>7027653</v>
+        <v>7027631</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2298,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,22 +2303,22 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2340,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132058228</v>
+        <v>132058259</v>
       </c>
       <c r="B17" t="n">
-        <v>79026</v>
+        <v>57912</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,37 +2346,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493154</v>
+        <v>493318</v>
       </c>
       <c r="R17" t="n">
-        <v>7027631</v>
+        <v>7027653</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132058265</v>
+        <v>132058239</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>80408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493521</v>
+        <v>492984</v>
       </c>
       <c r="R18" t="n">
-        <v>7027520</v>
+        <v>7027718</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132058244</v>
+        <v>132058265</v>
       </c>
       <c r="B19" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493117</v>
+        <v>493521</v>
       </c>
       <c r="R19" t="n">
-        <v>7027728</v>
+        <v>7027520</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132058252</v>
+        <v>132058244</v>
       </c>
       <c r="B20" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493154</v>
+        <v>493117</v>
       </c>
       <c r="R20" t="n">
-        <v>7027820</v>
+        <v>7027728</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,32 +2773,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132058239</v>
+        <v>132058252</v>
       </c>
       <c r="B21" t="n">
-        <v>80403</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492984</v>
+        <v>493154</v>
       </c>
       <c r="R21" t="n">
-        <v>7027718</v>
+        <v>7027820</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,7 +2883,7 @@
         <v>132058221</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>132058247</v>
       </c>
       <c r="B23" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>132058248</v>
       </c>
       <c r="B24" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>132058254</v>
       </c>
       <c r="B25" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>132058270</v>
       </c>
       <c r="B26" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>132058238</v>
       </c>
       <c r="B27" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>132058217</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>132058222</v>
       </c>
       <c r="B29" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>132058241</v>
       </c>
       <c r="B30" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>132058230</v>
       </c>
       <c r="B31" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>132058226</v>
       </c>
       <c r="B32" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>132058218</v>
       </c>
       <c r="B33" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 14196-2026 artfynd.xlsx
+++ b/artfynd/A 14196-2026 artfynd.xlsx
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132058263</v>
+        <v>132058235</v>
       </c>
       <c r="B14" t="n">
-        <v>80379</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493339</v>
+        <v>493016</v>
       </c>
       <c r="R14" t="n">
-        <v>7027668</v>
+        <v>7027677</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,11 +2095,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>igenvuxen betesmark?</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2116,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132058235</v>
+        <v>132058263</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>80379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493016</v>
+        <v>493339</v>
       </c>
       <c r="R15" t="n">
-        <v>7027677</v>
+        <v>7027668</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2186,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,6 +2202,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>igenvuxen betesmark?</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 14196-2026 artfynd.xlsx
+++ b/artfynd/A 14196-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>132058261</v>
       </c>
       <c r="B3" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132058269</v>
+        <v>132058268</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>91844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493330</v>
+        <v>493342</v>
       </c>
       <c r="R4" t="n">
-        <v>7027506</v>
+        <v>7027483</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132058268</v>
+        <v>132058269</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493342</v>
+        <v>493330</v>
       </c>
       <c r="R5" t="n">
-        <v>7027483</v>
+        <v>7027506</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>132058267</v>
       </c>
       <c r="B6" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>132058220</v>
       </c>
       <c r="B7" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>132058232</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132058242</v>
+        <v>132058215</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493069</v>
+        <v>493293</v>
       </c>
       <c r="R9" t="n">
-        <v>7027751</v>
+        <v>7027489</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1549,7 +1549,7 @@
         <v>132058249</v>
       </c>
       <c r="B10" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132058215</v>
+        <v>132058242</v>
       </c>
       <c r="B11" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493293</v>
+        <v>493069</v>
       </c>
       <c r="R11" t="n">
-        <v>7027489</v>
+        <v>7027751</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1783,7 +1783,7 @@
         <v>132058240</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>132058255</v>
       </c>
       <c r="B13" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132058235</v>
+        <v>132058263</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>80381</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493016</v>
+        <v>493339</v>
       </c>
       <c r="R14" t="n">
-        <v>7027677</v>
+        <v>7027668</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,6 +2095,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>igenvuxen betesmark?</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2111,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132058263</v>
+        <v>132058235</v>
       </c>
       <c r="B15" t="n">
-        <v>80379</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493339</v>
+        <v>493016</v>
       </c>
       <c r="R15" t="n">
-        <v>7027668</v>
+        <v>7027677</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2181,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,11 +2207,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>igenvuxen betesmark?</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132058228</v>
+        <v>132058259</v>
       </c>
       <c r="B16" t="n">
-        <v>79031</v>
+        <v>57914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,37 +2234,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493154</v>
+        <v>493318</v>
       </c>
       <c r="R16" t="n">
-        <v>7027631</v>
+        <v>7027653</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,22 +2308,22 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2335,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132058259</v>
+        <v>132058228</v>
       </c>
       <c r="B17" t="n">
-        <v>57912</v>
+        <v>79033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,42 +2351,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>hårkmon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493318</v>
+        <v>493154</v>
       </c>
       <c r="R17" t="n">
-        <v>7027653</v>
+        <v>7027631</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132058239</v>
+        <v>132058265</v>
       </c>
       <c r="B18" t="n">
-        <v>80408</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492984</v>
+        <v>493521</v>
       </c>
       <c r="R18" t="n">
-        <v>7027718</v>
+        <v>7027520</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132058265</v>
+        <v>132058244</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493521</v>
+        <v>493117</v>
       </c>
       <c r="R19" t="n">
-        <v>7027520</v>
+        <v>7027728</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132058244</v>
+        <v>132058252</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493117</v>
+        <v>493154</v>
       </c>
       <c r="R20" t="n">
-        <v>7027728</v>
+        <v>7027820</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,32 +2773,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132058252</v>
+        <v>132058239</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>80410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493154</v>
+        <v>492984</v>
       </c>
       <c r="R21" t="n">
-        <v>7027820</v>
+        <v>7027718</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,7 +2883,7 @@
         <v>132058221</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>132058247</v>
       </c>
       <c r="B23" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>132058248</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>132058254</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>132058270</v>
       </c>
       <c r="B26" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>132058238</v>
       </c>
       <c r="B27" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>132058217</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>132058222</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>132058241</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>132058230</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>132058226</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>132058218</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
